--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27592F88-EE38-4265-82EE-E3B0ABCB5548}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B1C456-FE6E-488E-B50E-3EA788F360EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="8" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -23,13 +23,13 @@
     <sheet name="04-02 R2" sheetId="1550" r:id="rId8"/>
     <sheet name="04-02 R3" sheetId="1551" r:id="rId9"/>
     <sheet name="(3)" sheetId="1552" r:id="rId10"/>
-    <sheet name="04-03 R1" sheetId="1553" r:id="rId11"/>
-    <sheet name="04-03 R2" sheetId="1554" r:id="rId12"/>
-    <sheet name="04-03 R3" sheetId="1555" r:id="rId13"/>
+    <sheet name="04-03 R1 HOLIDAY" sheetId="1553" r:id="rId11"/>
+    <sheet name="04-03 R2 HOLIDAY" sheetId="1554" r:id="rId12"/>
+    <sheet name="04-03 R3 HOLIDAY" sheetId="1555" r:id="rId13"/>
     <sheet name="(4)" sheetId="1556" r:id="rId14"/>
-    <sheet name="04-04 R1" sheetId="1557" r:id="rId15"/>
-    <sheet name="04-04 R2" sheetId="1558" r:id="rId16"/>
-    <sheet name="04-04 R3" sheetId="1559" r:id="rId17"/>
+    <sheet name="04-04 R1 HOLIDAY" sheetId="1557" r:id="rId15"/>
+    <sheet name="04-04 R2 HOLIDAY" sheetId="1558" r:id="rId16"/>
+    <sheet name="04-04 R3 HOLIDAY" sheetId="1559" r:id="rId17"/>
     <sheet name="(6)" sheetId="1560" r:id="rId18"/>
     <sheet name="04-06R1" sheetId="1561" r:id="rId19"/>
     <sheet name="04-06 R2" sheetId="1562" r:id="rId20"/>
@@ -50,12 +50,12 @@
     <definedName name="_xlnm.Print_Area" localSheetId="6">'04-02 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="7">'04-02 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'04-02 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="10">'04-03 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="11">'04-03 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="12">'04-03 R3'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="14">'04-04 R1'!$A$1:$Z$43</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="15">'04-04 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="16">'04-04 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'04-03 R1 HOLIDAY'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="11">'04-03 R2 HOLIDAY'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="12">'04-03 R3 HOLIDAY'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="14">'04-04 R1 HOLIDAY'!$A$1:$Z$43</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="15">'04-04 R2 HOLIDAY'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="16">'04-04 R3 HOLIDAY'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="19">'04-06 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="20">'04-06 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="18">'04-06R1'!$A$1:$Z$43</definedName>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1765" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="87">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -301,6 +301,42 @@
   </si>
   <si>
     <t>DATE ___________04/06/2026___________</t>
+  </si>
+  <si>
+    <t>18/20B</t>
+  </si>
+  <si>
+    <t>8/4B</t>
+  </si>
+  <si>
+    <t>2/12B</t>
+  </si>
+  <si>
+    <t>6/4B</t>
+  </si>
+  <si>
+    <t>16B</t>
+  </si>
+  <si>
+    <t>6/20B</t>
+  </si>
+  <si>
+    <t>1/19B</t>
+  </si>
+  <si>
+    <t>3/12B</t>
+  </si>
+  <si>
+    <t>3/4B</t>
+  </si>
+  <si>
+    <t>21/22B</t>
+  </si>
+  <si>
+    <t>7/3B</t>
+  </si>
+  <si>
+    <t>29/1B</t>
   </si>
 </sst>
 </file>
@@ -22762,7 +22798,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -23131,12 +23168,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>27</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -23148,10 +23189,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -23319,12 +23364,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>75</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -23336,10 +23385,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -23347,12 +23400,16 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>76</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -23364,10 +23421,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -23771,17 +23832,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>71</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>695</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>5</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -23957,17 +24028,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>7</v>
+      </c>
+      <c r="M31" s="23">
+        <v>51</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>0</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -23985,17 +24066,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>71</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>3</v>
+      </c>
+      <c r="M32" s="28">
+        <v>644</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>5</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -24135,16 +24226,32 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="F36" s="42">
+        <v>682</v>
+      </c>
+      <c r="G36" s="42">
+        <v>21</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>9</v>
+      </c>
+      <c r="J36" s="42">
+        <v>3</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
+      <c r="L36" s="42">
+        <v>4</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="O36" s="42">
+        <v>8</v>
+      </c>
       <c r="P36" s="42"/>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
@@ -24293,16 +24400,32 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="F42" s="42">
+        <v>682</v>
+      </c>
+      <c r="G42" s="42">
+        <v>21</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>9</v>
+      </c>
+      <c r="J42" s="42">
+        <v>3</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
+      <c r="L42" s="42">
+        <v>4</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="O42" s="42">
+        <v>8</v>
+      </c>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
       <c r="R42" s="82" t="s">
@@ -24346,7 +24469,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="90">
+        <f>1+8+1+1+1+71+3+644+5</f>
+        <v>735</v>
+      </c>
       <c r="D44" s="90"/>
       <c r="E44" s="90"/>
     </row>
@@ -24354,7 +24480,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="90"/>
+      <c r="C45" s="90">
+        <f>4</f>
+        <v>4</v>
+      </c>
       <c r="D45" s="90"/>
       <c r="E45" s="90"/>
     </row>
@@ -24753,12 +24882,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>80</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -24768,14 +24901,22 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14" t="s">
+        <v>82</v>
+      </c>
       <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -24941,12 +25082,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>79</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -24956,25 +25101,37 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>78</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -24984,14 +25141,22 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28" t="s">
+        <v>82</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56" t="s">
+        <v>82</v>
+      </c>
       <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -25393,17 +25558,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>2</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>71</v>
+      </c>
+      <c r="L24" s="14">
+        <v>18</v>
+      </c>
+      <c r="M24" s="14">
+        <v>432</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -25579,17 +25756,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>5</v>
+      </c>
+      <c r="M31" s="23">
+        <v>93</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>83</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -25607,17 +25796,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>2</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>70</v>
+      </c>
+      <c r="L32" s="28">
+        <v>13</v>
+      </c>
+      <c r="M32" s="28">
+        <v>339</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -25757,17 +25958,29 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>355</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>5</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>83</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
+      <c r="P36" s="42">
+        <v>6</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -25915,17 +26128,29 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>355</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>5</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>83</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
+      <c r="P42" s="42">
+        <v>6</v>
+      </c>
       <c r="Q42" s="43"/>
       <c r="R42" s="82" t="s">
         <v>54</v>
@@ -26006,7 +26231,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -26375,12 +26601,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>86</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -26390,14 +26620,22 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>2</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>4</v>
+      </c>
       <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -26563,12 +26801,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>2</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>85</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -26578,25 +26820,37 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>2</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>84</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -26606,14 +26860,22 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>2</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>3</v>
+      </c>
       <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -27015,17 +27277,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>112</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>17</v>
+      </c>
+      <c r="M24" s="14">
+        <v>598</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -27201,17 +27475,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>77</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>116</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>8</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -27229,17 +27515,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>35</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>2</v>
+      </c>
+      <c r="L32" s="28">
+        <v>17</v>
+      </c>
+      <c r="M32" s="28">
+        <v>482</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -27378,19 +27676,41 @@
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="E36" s="42">
+        <v>2</v>
+      </c>
+      <c r="F36" s="42">
+        <v>577</v>
+      </c>
+      <c r="G36" s="42">
+        <v>7</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="I36" s="42">
+        <v>4</v>
+      </c>
+      <c r="J36" s="42">
+        <v>2</v>
+      </c>
+      <c r="K36" s="42">
+        <v>7</v>
+      </c>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42">
+        <v>4</v>
+      </c>
+      <c r="N36" s="42">
+        <v>19</v>
+      </c>
+      <c r="O36" s="42">
+        <v>12</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>39</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -27536,19 +27856,41 @@
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="E42" s="42">
+        <v>2</v>
+      </c>
+      <c r="F42" s="42">
+        <v>577</v>
+      </c>
+      <c r="G42" s="42">
+        <v>7</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="I42" s="42">
+        <v>4</v>
+      </c>
+      <c r="J42" s="42">
+        <v>2</v>
+      </c>
+      <c r="K42" s="42">
+        <v>7</v>
+      </c>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42">
+        <v>4</v>
+      </c>
+      <c r="N42" s="42">
+        <v>19</v>
+      </c>
+      <c r="O42" s="42">
+        <v>12</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>39</v>
+      </c>
       <c r="R42" s="82" t="s">
         <v>54</v>
       </c>
@@ -27590,7 +27932,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="90">
+        <f>21+2+3+35+2+17+482</f>
+        <v>562</v>
+      </c>
       <c r="D44" s="90"/>
       <c r="E44" s="90"/>
     </row>
@@ -27598,7 +27943,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="90"/>
+      <c r="C45" s="90">
+        <f>22</f>
+        <v>22</v>
+      </c>
       <c r="D45" s="90"/>
       <c r="E45" s="90"/>
     </row>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1B1C456-FE6E-488E-B50E-3EA788F360EE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FAE2AC7-48E3-436D-8120-B97560780017}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="6" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -76,7 +76,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1783" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1798" uniqueCount="96">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -337,6 +337,33 @@
   </si>
   <si>
     <t>29/1B</t>
+  </si>
+  <si>
+    <t>24/1B</t>
+  </si>
+  <si>
+    <t>9/2B</t>
+  </si>
+  <si>
+    <t>33/3B</t>
+  </si>
+  <si>
+    <t>10B</t>
+  </si>
+  <si>
+    <t>13/6B</t>
+  </si>
+  <si>
+    <t>13/16B</t>
+  </si>
+  <si>
+    <t>12/2B</t>
+  </si>
+  <si>
+    <t>7/18B</t>
+  </si>
+  <si>
+    <t>14/20B</t>
   </si>
 </sst>
 </file>
@@ -29947,12 +29974,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>95</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -29964,12 +29995,20 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -30135,12 +30174,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>94</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -30152,23 +30195,35 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
+      <c r="X15" s="61">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>93</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -30180,12 +30235,20 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
+      <c r="X16" s="62">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -30587,14 +30650,22 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>22</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>7</v>
+      </c>
+      <c r="M24" s="14">
+        <v>409</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -30773,14 +30844,22 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>4</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>3</v>
+      </c>
+      <c r="M31" s="23">
+        <v>7</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -30801,14 +30880,22 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>18</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>4</v>
+      </c>
+      <c r="M32" s="28">
+        <v>402</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -30951,18 +31038,36 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="F36" s="42">
+        <v>147</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
+      <c r="I36" s="42">
+        <v>1</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>7</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="N36" s="42">
+        <v>4</v>
+      </c>
+      <c r="O36" s="42">
+        <v>2</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>10</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -31109,18 +31214,36 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="F42" s="42">
+        <v>147</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
+      <c r="I42" s="42">
+        <v>1</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>7</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="N42" s="42">
+        <v>4</v>
+      </c>
+      <c r="O42" s="42">
+        <v>2</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>10</v>
+      </c>
       <c r="R42" s="82" t="s">
         <v>54</v>
       </c>
@@ -31162,7 +31285,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="90">
+        <f>12+1+18+4+402</f>
+        <v>437</v>
+      </c>
       <c r="D44" s="90"/>
       <c r="E44" s="90"/>
     </row>
@@ -31170,7 +31296,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="90"/>
+      <c r="C45" s="90">
+        <f>2</f>
+        <v>2</v>
+      </c>
       <c r="D45" s="90"/>
       <c r="E45" s="90"/>
     </row>
@@ -31569,12 +31698,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>77</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>92</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -31584,12 +31719,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
+      <c r="U8" s="14">
+        <v>1</v>
+      </c>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -31757,12 +31898,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22" t="s">
+        <v>77</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>90</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -31772,12 +31919,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
-      <c r="U15" s="23"/>
+      <c r="U15" s="23">
+        <v>0</v>
+      </c>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -31785,12 +31938,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>91</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -31800,12 +31959,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
-      <c r="U16" s="28"/>
+      <c r="U16" s="28">
+        <v>1</v>
+      </c>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -32209,17 +32374,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>24</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>5</v>
+      </c>
+      <c r="M24" s="14">
+        <v>417</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -32395,17 +32572,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>19</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>5</v>
+      </c>
+      <c r="M31" s="23">
+        <v>64</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>83</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -32423,17 +32612,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>5</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>353</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -32573,18 +32774,30 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
+      <c r="F36" s="42">
+        <v>360</v>
+      </c>
+      <c r="G36" s="42">
+        <v>3</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>6</v>
+      </c>
+      <c r="P36" s="42">
+        <v>15</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>6</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -32731,18 +32944,30 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
+      <c r="F42" s="42">
+        <v>360</v>
+      </c>
+      <c r="G42" s="42">
+        <v>3</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>6</v>
+      </c>
+      <c r="P42" s="42">
+        <v>15</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>6</v>
+      </c>
       <c r="R42" s="82" t="s">
         <v>54</v>
       </c>
@@ -32784,7 +33009,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="90">
+        <f>1+13+1+5+353</f>
+        <v>373</v>
+      </c>
       <c r="D44" s="90"/>
       <c r="E44" s="90"/>
     </row>
@@ -32792,7 +33020,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="90"/>
+      <c r="C45" s="90">
+        <f>6</f>
+        <v>6</v>
+      </c>
       <c r="D45" s="90"/>
       <c r="E45" s="90"/>
     </row>
@@ -33191,12 +33422,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>2</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>1</v>
+      </c>
+      <c r="F8" s="14">
+        <v>1</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>89</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -33206,14 +33445,22 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14">
+        <v>2</v>
+      </c>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>5</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -33379,12 +33626,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>88</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -33394,25 +33649,41 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23">
+        <v>2</v>
+      </c>
       <c r="S15" s="23"/>
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>2</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>1</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>87</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -33422,14 +33693,22 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>3</v>
+      </c>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>0</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -33828,20 +34107,32 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>77</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>30</v>
+      </c>
+      <c r="M24" s="14">
+        <v>656</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -34014,20 +34305,32 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>1</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>3</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>8</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -34042,20 +34345,32 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>0</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>76</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>29</v>
+      </c>
+      <c r="M32" s="28">
+        <v>653</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -34194,19 +34509,39 @@
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="E36" s="42">
+        <v>1</v>
+      </c>
+      <c r="F36" s="42">
+        <v>757</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
+      <c r="H36" s="42">
+        <v>4</v>
+      </c>
+      <c r="I36" s="42">
+        <v>7</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="K36" s="42">
+        <v>5</v>
+      </c>
+      <c r="L36" s="42">
+        <v>6</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>17</v>
+      </c>
+      <c r="P36" s="42">
+        <v>8</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>13</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -34352,19 +34687,39 @@
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="E42" s="42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="42">
+        <v>757</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
+      <c r="H42" s="42">
+        <v>4</v>
+      </c>
+      <c r="I42" s="42">
+        <v>7</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="K42" s="42">
+        <v>5</v>
+      </c>
+      <c r="L42" s="42">
+        <v>6</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>17</v>
+      </c>
+      <c r="P42" s="42">
+        <v>8</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>13</v>
+      </c>
       <c r="R42" s="82" t="s">
         <v>54</v>
       </c>
@@ -34406,7 +34761,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="90"/>
+      <c r="C44" s="90">
+        <f>2+1+1+24+3+1+76+29+653</f>
+        <v>790</v>
+      </c>
       <c r="D44" s="90"/>
       <c r="E44" s="90"/>
     </row>
@@ -34414,7 +34772,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="90"/>
+      <c r="C45" s="90">
+        <f>1</f>
+        <v>1</v>
+      </c>
       <c r="D45" s="90"/>
       <c r="E45" s="90"/>
     </row>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C570F7ED-6625-4944-8836-A086E19B6E99}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE70155-ECAD-45F9-B4D1-5683F2AE725A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="14" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AE70155-ECAD-45F9-B4D1-5683F2AE725A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62A5557-134E-4054-8B8E-E20980AF0774}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="14" activeTab="20" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="24" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3921" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3927" uniqueCount="113">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -446,6 +446,24 @@
   <si>
     <t>10/6B</t>
   </si>
+  <si>
+    <t>ROUTE</t>
+  </si>
+  <si>
+    <t>2/18B</t>
+  </si>
+  <si>
+    <t>8/6B</t>
+  </si>
+  <si>
+    <t>35/20B</t>
+  </si>
+  <si>
+    <t>4/16B</t>
+  </si>
+  <si>
+    <t>31/4B</t>
+  </si>
 </sst>
 </file>
 
@@ -537,7 +555,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="42">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1058,6 +1076,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1065,7 +1137,7 @@
     <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="92">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1312,6 +1384,32 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1346,6 +1444,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="42" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3172,47 +3279,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -3444,12 +3551,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -4776,47 +4883,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -5048,12 +5155,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -5089,17 +5196,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -6398,47 +6505,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -6670,12 +6777,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -6711,17 +6818,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -8020,47 +8127,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -8292,12 +8399,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -8333,17 +8440,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -9640,47 +9747,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -9912,12 +10019,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11244,47 +11351,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -11516,12 +11623,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -11557,17 +11664,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -12866,47 +12973,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -13138,12 +13245,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -13179,17 +13286,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -14488,47 +14595,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -14760,12 +14867,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -14801,17 +14908,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -16108,47 +16215,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -16380,12 +16487,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -17773,47 +17880,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -18089,12 +18196,12 @@
       <c r="Q42" s="43">
         <v>22</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -18130,23 +18237,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>17+2+1+10+230+1+990</f>
         <v>1251</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <f>18</f>
         <v>18</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -19443,47 +19550,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -19715,12 +19822,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21077,47 +21184,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -21377,12 +21484,12 @@
         <v>13</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -21418,20 +21525,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>18+60+7+570</f>
         <v>655</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -22821,47 +22928,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -23141,12 +23248,12 @@
       <c r="Q42" s="43">
         <v>16</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -23182,22 +23289,22 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>10+4+1+108+19+541</f>
         <v>683</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <v>6</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -23251,6 +23358,7 @@
       <c r="B2" s="4" t="s">
         <v>67</v>
       </c>
+      <c r="V2" s="84"/>
     </row>
     <row r="3" spans="2:27" s="5" customFormat="1" ht="18" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
@@ -23519,8 +23627,10 @@
       </c>
     </row>
     <row r="7" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="8"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C7" s="86" t="s">
         <v>38</v>
       </c>
       <c r="D7" s="10" t="s">
@@ -23574,25 +23684,26 @@
       <c r="T7" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="U7" s="11" t="s">
+      <c r="U7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="V7" s="10" t="s">
+      <c r="V7" s="87" t="s">
         <v>65</v>
       </c>
-      <c r="W7" s="11" t="s">
+      <c r="W7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="X7" s="10" t="s">
+      <c r="X7" s="87" t="s">
         <v>17</v>
       </c>
-      <c r="Y7" s="10" t="s">
+      <c r="Y7" s="11" t="s">
         <v>19</v>
       </c>
+      <c r="Z7" s="82"/>
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="85"/>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
@@ -23610,8 +23721,8 @@
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
       <c r="T8" s="14"/>
-      <c r="U8" s="14"/>
-      <c r="V8" s="14"/>
+      <c r="U8" s="83"/>
+      <c r="V8" s="83"/>
       <c r="W8" s="14"/>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
@@ -24161,7 +24272,7 @@
     </row>
     <row r="23" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B23" s="37"/>
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="9" t="s">
         <v>16</v>
       </c>
       <c r="D23" s="10" t="s">
@@ -24209,20 +24320,20 @@
       <c r="R23" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="S23" s="11" t="s">
+      <c r="S23" s="81" t="s">
         <v>63</v>
       </c>
-      <c r="T23" s="11" t="s">
+      <c r="T23" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="U23" s="11" t="s">
+      <c r="U23" s="81" t="s">
         <v>36</v>
       </c>
-      <c r="V23" s="11" t="s">
+      <c r="V23" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
+      <c r="W23" s="80"/>
+      <c r="X23" s="81"/>
       <c r="Y23" s="11"/>
     </row>
     <row r="24" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -24494,47 +24605,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="97" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="101" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="95" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="95"/>
+      <c r="L34" s="101" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="95"/>
+      <c r="O34" s="102" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -24766,12 +24877,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -25197,11 +25308,15 @@
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="D8" s="14">
+        <v>2</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>25</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -25216,7 +25331,9 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -25385,11 +25502,15 @@
         <v>25</v>
       </c>
       <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>12</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -25404,7 +25525,9 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -25413,11 +25536,15 @@
         <v>26</v>
       </c>
       <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="D16" s="58">
+        <v>2</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>13</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -25432,7 +25559,9 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>3</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -25836,14 +25965,22 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>34</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>5</v>
+      </c>
+      <c r="M24" s="14">
+        <v>648</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -26022,14 +26159,22 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>1</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -26050,14 +26195,22 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>3</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>34</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>5</v>
+      </c>
+      <c r="M32" s="28">
+        <v>647</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -26098,47 +26251,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -26197,20 +26350,30 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>2</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>460</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="O36" s="42">
+        <v>5</v>
+      </c>
+      <c r="P36" s="42">
+        <v>8</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -26355,27 +26518,37 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>2</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>460</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="O42" s="42">
+        <v>5</v>
+      </c>
+      <c r="P42" s="42">
+        <v>8</v>
+      </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -26411,17 +26584,20 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99">
+        <f>2+13+3+3+34+5+647</f>
+        <v>707</v>
+      </c>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -26818,12 +26994,22 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
-      <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="G8" s="14">
+        <v>2</v>
+      </c>
+      <c r="H8" s="14">
+        <v>11</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -26835,10 +27021,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -27006,12 +27196,22 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
       <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="G15" s="23">
+        <v>1</v>
+      </c>
+      <c r="H15" s="23" t="s">
+        <v>108</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -27023,10 +27223,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -27034,12 +27238,22 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
       <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="G16" s="28">
+        <v>1</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>109</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -27051,10 +27265,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>2</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -27455,18 +27673,34 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
+      <c r="D24" s="14">
+        <v>1</v>
+      </c>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>1</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>48</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="K24" s="14">
+        <v>1</v>
+      </c>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>375</v>
+      </c>
+      <c r="N24" s="14">
+        <v>2</v>
+      </c>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
@@ -27641,18 +27875,34 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
+      <c r="C31" s="22">
+        <v>1</v>
+      </c>
+      <c r="D31" s="23">
+        <v>0</v>
+      </c>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>23</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
+      <c r="K31" s="23">
+        <v>1</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>0</v>
+      </c>
+      <c r="N31" s="23">
+        <v>0</v>
+      </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
       <c r="Q31" s="23"/>
@@ -27669,18 +27919,34 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
+      <c r="C32" s="26">
+        <v>0</v>
+      </c>
+      <c r="D32" s="27">
+        <v>1</v>
+      </c>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>25</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>375</v>
+      </c>
+      <c r="N32" s="28">
+        <v>2</v>
+      </c>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
       <c r="Q32" s="28"/>
@@ -27720,47 +27986,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -27822,18 +28088,38 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="F36" s="42">
+        <v>372</v>
+      </c>
+      <c r="G36" s="42">
+        <v>32</v>
+      </c>
+      <c r="H36" s="42">
+        <v>3</v>
+      </c>
+      <c r="I36" s="42">
+        <v>6</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>4</v>
+      </c>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>7</v>
+      </c>
+      <c r="P36" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>15</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -27980,24 +28266,44 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="F42" s="42">
+        <v>372</v>
+      </c>
+      <c r="G42" s="42">
+        <v>32</v>
+      </c>
+      <c r="H42" s="42">
+        <v>3</v>
+      </c>
+      <c r="I42" s="42">
+        <v>6</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>4</v>
+      </c>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="O42" s="42">
+        <v>7</v>
+      </c>
+      <c r="P42" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>15</v>
+      </c>
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -28033,17 +28339,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99">
+        <f>2+1+8+2+1+25+10+375+2</f>
+        <v>426</v>
+      </c>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99">
+        <f>6</f>
+        <v>6</v>
+      </c>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -28442,10 +28754,16 @@
       <c r="B8" s="12"/>
       <c r="C8" s="13"/>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-      <c r="F8" s="14"/>
+      <c r="E8" s="14">
+        <v>18</v>
+      </c>
+      <c r="F8" s="14">
+        <v>13</v>
+      </c>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>110</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -28460,9 +28778,15 @@
       <c r="T8" s="14"/>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
-      <c r="X8" s="59"/>
-      <c r="Y8" s="15"/>
+      <c r="W8" s="14">
+        <v>9</v>
+      </c>
+      <c r="X8" s="59">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="12" t="s">
@@ -28630,10 +28954,16 @@
       </c>
       <c r="C15" s="22"/>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
+      <c r="F15" s="23">
+        <v>0</v>
+      </c>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>111</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -28648,9 +28978,15 @@
       <c r="T15" s="23"/>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
-      <c r="X15" s="61"/>
-      <c r="Y15" s="24"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
+      <c r="X15" s="61">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="24">
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="2:27" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="25" t="s">
@@ -28658,10 +28994,16 @@
       </c>
       <c r="C16" s="57"/>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
-      <c r="F16" s="27"/>
+      <c r="E16" s="27">
+        <v>18</v>
+      </c>
+      <c r="F16" s="27">
+        <v>13</v>
+      </c>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>112</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -28676,9 +29018,15 @@
       <c r="T16" s="28"/>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
-      <c r="X16" s="62"/>
-      <c r="Y16" s="29"/>
+      <c r="W16" s="56">
+        <v>9</v>
+      </c>
+      <c r="X16" s="62">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="2:25" s="5" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="30"/>
@@ -29077,22 +29425,34 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>109</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>10</v>
+      </c>
+      <c r="M24" s="14">
+        <v>756</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
+      <c r="R24" s="14">
+        <v>6</v>
+      </c>
       <c r="S24" s="14"/>
       <c r="T24" s="14"/>
       <c r="U24" s="14"/>
@@ -29263,22 +29623,34 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>1</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>0</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>8</v>
+      </c>
       <c r="Q31" s="23"/>
-      <c r="R31" s="23"/>
+      <c r="R31" s="23">
+        <v>0</v>
+      </c>
       <c r="S31" s="23"/>
       <c r="T31" s="23"/>
       <c r="U31" s="23"/>
@@ -29291,22 +29663,34 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>1</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>108</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>9</v>
+      </c>
+      <c r="M32" s="28">
+        <v>756</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
+      <c r="R32" s="28">
+        <v>6</v>
+      </c>
       <c r="S32" s="28"/>
       <c r="T32" s="28"/>
       <c r="U32" s="28"/>
@@ -29342,47 +29726,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -29441,21 +29825,35 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>5</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>896</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>15</v>
+      </c>
       <c r="J36" s="42"/>
       <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="L36" s="42">
+        <v>9</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>12</v>
+      </c>
+      <c r="P36" s="42">
+        <v>35</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>4</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -29599,27 +29997,41 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>5</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>896</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>15</v>
+      </c>
       <c r="J42" s="42"/>
       <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="L42" s="42">
+        <v>9</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="O42" s="42">
+        <v>12</v>
+      </c>
+      <c r="P42" s="42">
+        <v>35</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>4</v>
+      </c>
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -29655,17 +30067,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99">
+        <f>18+13+31+9+1+1+1+108+9+756+6</f>
+        <v>953</v>
+      </c>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99">
+        <f>4</f>
+        <v>4</v>
+      </c>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -30962,47 +31380,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -31234,12 +31652,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -32566,47 +32984,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -32838,12 +33256,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -32879,17 +33297,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -34188,47 +34606,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -34460,12 +34878,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -34501,17 +34919,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -35810,47 +36228,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -36082,12 +36500,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -36123,17 +36541,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -37487,47 +37905,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -37791,12 +38209,12 @@
       </c>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -37832,23 +38250,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>1+8+1+1+1+71+3+644+5</f>
         <v>735</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <f>4</f>
         <v>4</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -39145,47 +39563,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -39417,12 +39835,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -40749,47 +41167,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -41021,12 +41439,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -41062,17 +41480,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -42371,47 +42789,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -42643,12 +43061,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -42684,17 +43102,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -43993,47 +44411,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -44265,12 +44683,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -44306,17 +44724,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -45613,47 +46031,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -45885,12 +46303,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -47217,47 +47635,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -47489,12 +47907,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -47530,17 +47948,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -48839,47 +49257,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -49111,12 +49529,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -49152,17 +49570,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -50461,47 +50879,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -50733,12 +51151,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -50774,17 +51192,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -52081,47 +52499,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -52353,12 +52771,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -53685,47 +54103,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -53957,12 +54375,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -53998,17 +54416,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -55379,47 +55797,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -55675,12 +56093,12 @@
         <v>6</v>
       </c>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -55716,17 +56134,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -57025,47 +57443,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -57297,12 +57715,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -57338,17 +57756,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -58647,47 +59065,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -58919,12 +59337,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -58960,17 +59378,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -60267,47 +60685,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -60539,12 +60957,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -61871,47 +62289,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -62143,12 +62561,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -62184,17 +62602,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -63493,47 +63911,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -63765,12 +64183,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -63806,17 +64224,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -65115,47 +65533,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -65387,12 +65805,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -65428,17 +65846,17 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="C45" s="99"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -66810,47 +67228,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -67126,12 +67544,12 @@
       <c r="Q42" s="43">
         <v>39</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -67167,23 +67585,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>21+2+3+35+2+17+482</f>
         <v>562</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <f>22</f>
         <v>22</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -68480,47 +68898,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -68752,12 +69170,12 @@
       <c r="O42" s="42"/>
       <c r="P42" s="42"/>
       <c r="Q42" s="43"/>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -70144,47 +70562,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -70452,12 +70870,12 @@
       <c r="Q42" s="43">
         <v>10</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -70493,23 +70911,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>12+1+18+4+402</f>
         <v>437</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <f>2</f>
         <v>2</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -71880,47 +72298,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -72176,12 +72594,12 @@
       <c r="Q42" s="43">
         <v>6</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -72217,23 +72635,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>1+13+1+5+353</f>
         <v>373</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <f>6</f>
         <v>6</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -73616,47 +74034,47 @@
       <c r="Y33" s="31"/>
     </row>
     <row r="34" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="85" t="s">
+      <c r="B34" s="93" t="s">
         <v>43</v>
       </c>
-      <c r="C34" s="87" t="s">
+      <c r="C34" s="95" t="s">
         <v>21</v>
       </c>
-      <c r="D34" s="87"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="89" t="s">
+      <c r="D34" s="95"/>
+      <c r="E34" s="96"/>
+      <c r="F34" s="97" t="s">
         <v>44</v>
       </c>
-      <c r="G34" s="87"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="89" t="s">
+      <c r="G34" s="95"/>
+      <c r="H34" s="96"/>
+      <c r="I34" s="97" t="s">
         <v>45</v>
       </c>
-      <c r="J34" s="87"/>
-      <c r="K34" s="88"/>
-      <c r="L34" s="89" t="s">
+      <c r="J34" s="95"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="97" t="s">
         <v>46</v>
       </c>
-      <c r="M34" s="87"/>
-      <c r="N34" s="88"/>
-      <c r="O34" s="90" t="s">
+      <c r="M34" s="95"/>
+      <c r="N34" s="96"/>
+      <c r="O34" s="98" t="s">
         <v>47</v>
       </c>
-      <c r="P34" s="90"/>
-      <c r="Q34" s="90"/>
-      <c r="R34" s="80" t="s">
+      <c r="P34" s="98"/>
+      <c r="Q34" s="98"/>
+      <c r="R34" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="S34" s="81"/>
-      <c r="T34" s="81"/>
-      <c r="U34" s="82"/>
+      <c r="S34" s="89"/>
+      <c r="T34" s="89"/>
+      <c r="U34" s="90"/>
       <c r="V34" s="66"/>
       <c r="W34" s="3"/>
       <c r="X34" s="3"/>
       <c r="Y34" s="3"/>
     </row>
     <row r="35" spans="2:25" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B35" s="86"/>
+      <c r="B35" s="94"/>
       <c r="C35" s="50" t="s">
         <v>49</v>
       </c>
@@ -73928,12 +74346,12 @@
       <c r="Q42" s="43">
         <v>13</v>
       </c>
-      <c r="R42" s="83" t="s">
+      <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
-      <c r="S42" s="84"/>
-      <c r="T42" s="84"/>
-      <c r="U42" s="84"/>
+      <c r="S42" s="92"/>
+      <c r="T42" s="92"/>
+      <c r="U42" s="92"/>
       <c r="V42" s="3"/>
       <c r="W42" s="3"/>
       <c r="X42" s="3"/>
@@ -73969,23 +74387,23 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="91">
+      <c r="C44" s="99">
         <f>2+1+1+24+3+1+76+29+653</f>
         <v>790</v>
       </c>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
     </row>
     <row r="45" spans="2:25" x14ac:dyDescent="0.25">
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="91">
+      <c r="C45" s="99">
         <f>1</f>
         <v>1</v>
       </c>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
+      <c r="D45" s="99"/>
+      <c r="E45" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62A5557-134E-4054-8B8E-E20980AF0774}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18D0E94-7B90-4D3F-B023-2E5FB1A62C18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="24" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="28" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3927" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="118">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -463,6 +463,21 @@
   </si>
   <si>
     <t>31/4B</t>
+  </si>
+  <si>
+    <t>12/4B</t>
+  </si>
+  <si>
+    <t>7/4B</t>
+  </si>
+  <si>
+    <t>24/16B</t>
+  </si>
+  <si>
+    <t>4/4B</t>
+  </si>
+  <si>
+    <t>20/12B</t>
   </si>
 </sst>
 </file>
@@ -28383,7 +28398,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -32087,7 +32103,9 @@
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>17</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -32275,7 +32293,9 @@
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>2</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -32303,7 +32323,9 @@
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28">
+        <v>15</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -32729,7 +32751,9 @@
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
       <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="M24" s="14">
+        <v>540</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -32915,7 +32939,9 @@
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
       <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="M31" s="23">
+        <v>0</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -32943,7 +32969,9 @@
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
       <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="M32" s="28">
+        <v>540</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -33086,17 +33114,27 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
+      <c r="F36" s="42">
+        <v>507</v>
+      </c>
+      <c r="G36" s="42">
+        <v>5</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
       <c r="I36" s="42"/>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="42">
+        <v>7</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
       <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
+      <c r="P36" s="42">
+        <v>17</v>
+      </c>
       <c r="Q36" s="43"/>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
@@ -33244,17 +33282,27 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
+      <c r="F42" s="42">
+        <v>507</v>
+      </c>
+      <c r="G42" s="42">
+        <v>5</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
       <c r="I42" s="42"/>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="42">
+        <v>7</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
       <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
+      <c r="P42" s="42">
+        <v>17</v>
+      </c>
       <c r="Q42" s="43"/>
       <c r="R42" s="91" t="s">
         <v>54</v>
@@ -33297,7 +33345,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>15+540</f>
+        <v>555</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -33704,12 +33755,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -33719,12 +33776,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -33892,12 +33955,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23">
+        <v>5</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -33907,12 +33976,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>2</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -33920,12 +33995,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>114</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -33935,12 +34016,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>0</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -34344,17 +34431,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>48</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>8</v>
+      </c>
+      <c r="M24" s="14">
+        <v>388</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -34530,17 +34629,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>8</v>
+      </c>
+      <c r="M31" s="23">
+        <v>61</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>83</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -34558,17 +34669,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>48</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>0</v>
+      </c>
+      <c r="M32" s="28">
+        <v>327</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -34708,18 +34831,32 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>406</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="42">
+        <v>1</v>
+      </c>
       <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>4</v>
+      </c>
+      <c r="P36" s="42">
+        <v>7</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>8</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -34866,18 +35003,32 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>406</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="42">
+        <v>1</v>
+      </c>
       <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>4</v>
+      </c>
+      <c r="P42" s="42">
+        <v>7</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>8</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -34919,7 +35070,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>7+48+327</f>
+        <v>382</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -34927,7 +35081,9 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="99"/>
+      <c r="C45" s="99">
+        <v>4</v>
+      </c>
       <c r="D45" s="99"/>
       <c r="E45" s="99"/>
     </row>
@@ -34957,7 +35113,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -35326,12 +35483,20 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
+      <c r="E8" s="14">
+        <v>2</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>115</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -35343,10 +35508,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>5</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -35514,12 +35683,20 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>116</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -35531,10 +35708,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -35542,12 +35723,20 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
+      <c r="E16" s="27">
+        <v>2</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>117</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -35559,10 +35748,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>4</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -35966,17 +36159,27 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>2</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>109</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>11</v>
+      </c>
+      <c r="M24" s="14">
+        <v>602</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -36152,17 +36355,27 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>0</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>15</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>1</v>
+      </c>
+      <c r="M31" s="23">
+        <v>2</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>8</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -36180,17 +36393,27 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>2</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>94</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>10</v>
+      </c>
+      <c r="M32" s="28">
+        <v>600</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -36327,21 +36550,37 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>2</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
+      <c r="F36" s="42">
+        <v>703</v>
+      </c>
       <c r="G36" s="42"/>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="I36" s="42">
+        <v>8</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="K36" s="42">
+        <v>10</v>
+      </c>
       <c r="L36" s="42"/>
       <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="N36" s="42">
+        <v>3</v>
+      </c>
+      <c r="O36" s="42">
+        <v>26</v>
+      </c>
+      <c r="P36" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>10</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -36485,21 +36724,37 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>2</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
+      <c r="F42" s="42">
+        <v>703</v>
+      </c>
       <c r="G42" s="42"/>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="I42" s="42">
+        <v>8</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="K42" s="42">
+        <v>10</v>
+      </c>
       <c r="L42" s="42"/>
       <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="N42" s="42">
+        <v>3</v>
+      </c>
+      <c r="O42" s="42">
+        <v>26</v>
+      </c>
+      <c r="P42" s="42">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>10</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -36541,7 +36796,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>2+20+4+2+94+10+600</f>
+        <v>732</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -36549,7 +36807,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="99"/>
+      <c r="C45" s="99">
+        <f>12</f>
+        <v>12</v>
+      </c>
       <c r="D45" s="99"/>
       <c r="E45" s="99"/>
     </row>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D18D0E94-7B90-4D3F-B023-2E5FB1A62C18}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09FF535-CF94-40E6-B27D-FFC8EAD53D50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="28" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="27" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A09FF535-CF94-40E6-B27D-FFC8EAD53D50}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6002351A-C281-49B4-AB8E-B54E2341F469}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="17" activeTab="27" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="32" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3938" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="126">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -478,6 +478,30 @@
   </si>
   <si>
     <t>20/12B</t>
+  </si>
+  <si>
+    <t>24/4B</t>
+  </si>
+  <si>
+    <t>6/2B</t>
+  </si>
+  <si>
+    <t>18/2B</t>
+  </si>
+  <si>
+    <t>6/3B</t>
+  </si>
+  <si>
+    <t>17/21B</t>
+  </si>
+  <si>
+    <t>1/12B</t>
+  </si>
+  <si>
+    <t>4/12B</t>
+  </si>
+  <si>
+    <t>11/20B</t>
   </si>
 </sst>
 </file>
@@ -40157,7 +40181,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -40526,12 +40551,16 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13">
+        <v>3</v>
+      </c>
       <c r="D8" s="14"/>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>24</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -40543,10 +40572,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>3</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>6</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -40714,12 +40747,16 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>3</v>
+      </c>
       <c r="D15" s="23"/>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>122</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -40731,10 +40768,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>3</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23" t="s">
+        <v>124</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -40742,12 +40783,16 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
       <c r="D16" s="58"/>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>121</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -40759,10 +40804,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56" t="s">
+        <v>123</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -41166,14 +41215,22 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>20</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>2</v>
+      </c>
+      <c r="M24" s="14">
+        <v>546</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
@@ -41352,14 +41409,22 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>11</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
@@ -41380,14 +41445,22 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>20</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>535</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
@@ -41529,19 +41602,43 @@
       </c>
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="E36" s="42">
+        <v>1</v>
+      </c>
+      <c r="F36" s="42">
+        <v>509</v>
+      </c>
+      <c r="G36" s="42">
+        <v>22</v>
+      </c>
+      <c r="H36" s="42">
+        <v>2</v>
+      </c>
+      <c r="I36" s="42">
+        <v>4</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>4</v>
+      </c>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>8</v>
+      </c>
+      <c r="O36" s="42">
+        <v>11</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>29</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -41687,19 +41784,43 @@
       </c>
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="E42" s="42">
+        <v>1</v>
+      </c>
+      <c r="F42" s="42">
+        <v>509</v>
+      </c>
+      <c r="G42" s="42">
+        <v>22</v>
+      </c>
+      <c r="H42" s="42">
+        <v>2</v>
+      </c>
+      <c r="I42" s="42">
+        <v>4</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>4</v>
+      </c>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>8</v>
+      </c>
+      <c r="O42" s="42">
+        <v>11</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>29</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -41779,7 +41900,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -42148,12 +42270,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14">
+        <v>15</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -42163,12 +42291,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>2</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -42336,12 +42470,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>83</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -42351,12 +42491,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>1</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -42364,12 +42510,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>125</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -42379,12 +42531,18 @@
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -42788,17 +42946,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>27</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>8</v>
+      </c>
+      <c r="M24" s="14">
+        <v>384</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -42974,17 +43144,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>3</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>15</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>5</v>
+      </c>
+      <c r="M31" s="23">
+        <v>67</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>83</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -43002,17 +43184,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>0</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>12</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>3</v>
+      </c>
+      <c r="M32" s="28">
+        <v>317</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -43152,18 +43346,38 @@
       <c r="C36" s="46"/>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
+      <c r="F36" s="42">
+        <v>330</v>
+      </c>
+      <c r="G36" s="42">
+        <v>1</v>
+      </c>
       <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
+      <c r="I36" s="42">
+        <v>2</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>8</v>
+      </c>
       <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>5</v>
+      </c>
+      <c r="O36" s="42">
+        <v>4</v>
+      </c>
+      <c r="P36" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>23</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -43310,18 +43524,38 @@
       <c r="C42" s="46"/>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
+      <c r="F42" s="42">
+        <v>330</v>
+      </c>
+      <c r="G42" s="42">
+        <v>1</v>
+      </c>
       <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
+      <c r="I42" s="42">
+        <v>2</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>8</v>
+      </c>
       <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>5</v>
+      </c>
+      <c r="O42" s="42">
+        <v>4</v>
+      </c>
+      <c r="P42" s="42">
+        <v>9</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>23</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -43363,7 +43597,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>11+1+12+3+317</f>
+        <v>344</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -43371,7 +43608,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="99"/>
+      <c r="C45" s="99">
+        <f>20</f>
+        <v>20</v>
+      </c>
       <c r="D45" s="99"/>
       <c r="E45" s="99"/>
     </row>
@@ -43770,12 +44010,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>118</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -43787,10 +44033,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>3</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -43958,12 +44208,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22">
+        <v>0</v>
+      </c>
+      <c r="D15" s="23">
+        <v>0</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>119</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -43975,10 +44231,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -43986,12 +44246,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>1</v>
+      </c>
+      <c r="D16" s="58">
+        <v>1</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>120</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -44003,10 +44269,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>1</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>3</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -44407,20 +44677,30 @@
       <c r="B24" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="13"/>
+      <c r="C24" s="13">
+        <v>1</v>
+      </c>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="14"/>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>117</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
       <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="L24" s="14">
+        <v>36</v>
+      </c>
+      <c r="M24" s="14">
+        <v>542</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14">
+        <v>8</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -44593,20 +44873,30 @@
       <c r="B31" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C31" s="22"/>
+      <c r="C31" s="22">
+        <v>0</v>
+      </c>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
       <c r="F31" s="23"/>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>98</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
       <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="L31" s="23">
+        <v>4</v>
+      </c>
+      <c r="M31" s="23">
+        <v>19</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23">
+        <v>8</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -44621,20 +44911,30 @@
       <c r="B32" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="26"/>
+      <c r="C32" s="26">
+        <v>1</v>
+      </c>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
       <c r="F32" s="27"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>19</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
       <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="L32" s="28">
+        <v>32</v>
+      </c>
+      <c r="M32" s="28">
+        <v>523</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>0</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -44771,21 +45071,47 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
+      <c r="C36" s="46">
+        <v>6</v>
+      </c>
       <c r="D36" s="41"/>
       <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="F36" s="42">
+        <v>650</v>
+      </c>
+      <c r="G36" s="42">
+        <v>18</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>41</v>
+      </c>
+      <c r="J36" s="42">
+        <v>3</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
+      <c r="L36" s="42">
+        <v>3</v>
+      </c>
+      <c r="M36" s="42">
+        <v>3</v>
+      </c>
+      <c r="N36" s="42">
+        <v>1</v>
+      </c>
+      <c r="O36" s="42">
+        <v>14</v>
+      </c>
+      <c r="P36" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>10</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -44929,21 +45255,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
+      <c r="C42" s="46">
+        <v>6</v>
+      </c>
       <c r="D42" s="41"/>
       <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="F42" s="42">
+        <v>650</v>
+      </c>
+      <c r="G42" s="42">
+        <v>18</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>41</v>
+      </c>
+      <c r="J42" s="42">
+        <v>3</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
+      <c r="L42" s="42">
+        <v>3</v>
+      </c>
+      <c r="M42" s="42">
+        <v>3</v>
+      </c>
+      <c r="N42" s="42">
+        <v>1</v>
+      </c>
+      <c r="O42" s="42">
+        <v>14</v>
+      </c>
+      <c r="P42" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>10</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -44985,7 +45337,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>1+1+18+1+3+1+19+32+523</f>
+        <v>599</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -44993,7 +45348,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="99"/>
+      <c r="C45" s="99">
+        <f>2</f>
+        <v>2</v>
+      </c>
       <c r="D45" s="99"/>
       <c r="E45" s="99"/>
     </row>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6002351A-C281-49B4-AB8E-B54E2341F469}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B07B29-8AD7-477D-8856-EF692F5D0194}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="32" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="35" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
   <sheets>
     <sheet name="CSR | APRIL" sheetId="902" r:id="rId1"/>
@@ -49,7 +49,7 @@
     <sheet name="(10)" sheetId="1576" r:id="rId34"/>
     <sheet name="04-10 R1" sheetId="1577" r:id="rId35"/>
     <sheet name="04-10 R2" sheetId="1578" r:id="rId36"/>
-    <sheet name="04-10 R3" sheetId="1579" r:id="rId37"/>
+    <sheet name="04-10 R3 NO TRIP" sheetId="1579" r:id="rId37"/>
     <sheet name="(11)" sheetId="1580" r:id="rId38"/>
     <sheet name="04-11 R1" sheetId="1581" r:id="rId39"/>
     <sheet name="04-11 R2" sheetId="1582" r:id="rId40"/>
@@ -100,7 +100,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="32">'04-09 R3'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="34">'04-10 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="35">'04-10 R2'!$A$1:$V$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="36">'04-10 R3'!$A$1:$V$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="36">'04-10 R3 NO TRIP'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="38">'04-11 R1'!$A$1:$Z$43</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="39">'04-11 R2'!$A$1:$V$44</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="40">'04-11 R3'!$A$1:$V$44</definedName>
@@ -124,7 +124,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3953" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3977" uniqueCount="136">
   <si>
     <t>CHECKER STOCK REPORT</t>
   </si>
@@ -502,6 +502,36 @@
   </si>
   <si>
     <t>11/20B</t>
+  </si>
+  <si>
+    <t>3/2B</t>
+  </si>
+  <si>
+    <t>2/2B</t>
+  </si>
+  <si>
+    <t>14/11B</t>
+  </si>
+  <si>
+    <t>3/10B</t>
+  </si>
+  <si>
+    <t>4/10B</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>10/9B</t>
+  </si>
+  <si>
+    <t>15/4B</t>
+  </si>
+  <si>
+    <t>17B</t>
+  </si>
+  <si>
+    <t>2/4B</t>
   </si>
 </sst>
 </file>
@@ -46983,7 +47013,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -47352,12 +47383,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
+      <c r="C8" s="13" t="s">
+        <v>126</v>
+      </c>
       <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
+      <c r="E8" s="14">
+        <v>5</v>
+      </c>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>122</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -47369,10 +47406,14 @@
       <c r="Q8" s="14"/>
       <c r="R8" s="14"/>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14" t="s">
+        <v>130</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14" t="s">
+        <v>124</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -47540,12 +47581,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="22">
+        <v>1</v>
+      </c>
       <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="E15" s="23">
+        <v>0</v>
+      </c>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>128</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -47557,10 +47604,14 @@
       <c r="Q15" s="23"/>
       <c r="R15" s="23"/>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>0</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -47568,12 +47619,18 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
+      <c r="C16" s="57" t="s">
+        <v>127</v>
+      </c>
       <c r="D16" s="58"/>
-      <c r="E16" s="27"/>
+      <c r="E16" s="27">
+        <v>5</v>
+      </c>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>129</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
       <c r="K16" s="56"/>
@@ -47585,10 +47642,14 @@
       <c r="Q16" s="28"/>
       <c r="R16" s="28"/>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28" t="s">
+        <v>130</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56" t="s">
+        <v>124</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -47990,17 +48051,33 @@
         <v>23</v>
       </c>
       <c r="C24" s="13"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="D24" s="14">
+        <v>2</v>
+      </c>
+      <c r="E24" s="14">
+        <v>1</v>
+      </c>
+      <c r="F24" s="14" t="s">
+        <v>114</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>22</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
+      <c r="K24" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="L24" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="M24" s="14">
+        <v>331</v>
+      </c>
+      <c r="N24" s="14">
+        <v>1</v>
+      </c>
       <c r="O24" s="14"/>
       <c r="P24" s="14"/>
       <c r="Q24" s="14"/>
@@ -48176,17 +48253,33 @@
         <v>25</v>
       </c>
       <c r="C31" s="22"/>
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="D31" s="23">
+        <v>0</v>
+      </c>
+      <c r="E31" s="23">
+        <v>0</v>
+      </c>
+      <c r="F31" s="23">
+        <v>1</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>0</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
-      <c r="N31" s="23"/>
+      <c r="K31" s="23">
+        <v>0</v>
+      </c>
+      <c r="L31" s="23">
+        <v>0</v>
+      </c>
+      <c r="M31" s="23">
+        <v>15</v>
+      </c>
+      <c r="N31" s="23">
+        <v>0</v>
+      </c>
       <c r="O31" s="23"/>
       <c r="P31" s="23"/>
       <c r="Q31" s="23"/>
@@ -48204,17 +48297,33 @@
         <v>26</v>
       </c>
       <c r="C32" s="26"/>
-      <c r="D32" s="27"/>
-      <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="D32" s="27">
+        <v>2</v>
+      </c>
+      <c r="E32" s="27">
+        <v>1</v>
+      </c>
+      <c r="F32" s="27" t="s">
+        <v>78</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>22</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
+      <c r="K32" s="28" t="s">
+        <v>131</v>
+      </c>
+      <c r="L32" s="28" t="s">
+        <v>132</v>
+      </c>
+      <c r="M32" s="28">
+        <v>316</v>
+      </c>
+      <c r="N32" s="28">
+        <v>1</v>
+      </c>
       <c r="O32" s="23"/>
       <c r="P32" s="28"/>
       <c r="Q32" s="28"/>
@@ -48353,21 +48462,47 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
+      <c r="C36" s="46">
+        <v>6</v>
+      </c>
+      <c r="D36" s="41">
+        <v>4</v>
+      </c>
+      <c r="E36" s="42">
+        <v>18</v>
+      </c>
+      <c r="F36" s="42">
+        <v>318</v>
+      </c>
+      <c r="G36" s="42">
+        <v>19</v>
+      </c>
+      <c r="H36" s="42">
+        <v>1</v>
+      </c>
+      <c r="I36" s="42">
+        <v>12</v>
+      </c>
       <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
+      <c r="K36" s="42">
+        <v>1</v>
+      </c>
+      <c r="L36" s="42">
+        <v>7</v>
+      </c>
+      <c r="M36" s="42">
+        <v>1</v>
+      </c>
+      <c r="N36" s="42">
+        <v>1</v>
+      </c>
+      <c r="O36" s="42">
+        <v>3</v>
+      </c>
       <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="Q36" s="43">
+        <v>69</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -48511,21 +48646,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
+      <c r="C42" s="46">
+        <v>6</v>
+      </c>
+      <c r="D42" s="41">
+        <v>4</v>
+      </c>
+      <c r="E42" s="42">
+        <v>18</v>
+      </c>
+      <c r="F42" s="42">
+        <v>318</v>
+      </c>
+      <c r="G42" s="42">
+        <v>19</v>
+      </c>
+      <c r="H42" s="42">
+        <v>1</v>
+      </c>
+      <c r="I42" s="42">
+        <v>12</v>
+      </c>
       <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
-      <c r="M42" s="42"/>
-      <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
+      <c r="K42" s="42">
+        <v>1</v>
+      </c>
+      <c r="L42" s="42">
+        <v>7</v>
+      </c>
+      <c r="M42" s="42">
+        <v>1</v>
+      </c>
+      <c r="N42" s="42">
+        <v>1</v>
+      </c>
+      <c r="O42" s="42">
+        <v>3</v>
+      </c>
       <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="Q42" s="43">
+        <v>69</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -48567,7 +48728,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>2+5+3+4+4+2+1+6+22+10+316+1</f>
+        <v>376</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -48575,7 +48739,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="99"/>
+      <c r="C45" s="99">
+        <f>2+10+10+12+6+4+9</f>
+        <v>53</v>
+      </c>
       <c r="D45" s="99"/>
       <c r="E45" s="99"/>
     </row>
@@ -48605,7 +48772,8 @@
   <cols>
     <col min="1" max="1" width="1.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="14.42578125" style="2" customWidth="1"/>
-    <col min="3" max="8" width="5.7109375" style="2" customWidth="1"/>
+    <col min="3" max="7" width="5.7109375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="7" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="13" width="5.7109375" style="2" customWidth="1"/>
@@ -48974,12 +49142,18 @@
     </row>
     <row r="8" spans="2:27" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="14"/>
+      <c r="C8" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="14">
+        <v>1</v>
+      </c>
       <c r="E8" s="14"/>
       <c r="F8" s="14"/>
       <c r="G8" s="14"/>
-      <c r="H8" s="14"/>
+      <c r="H8" s="14" t="s">
+        <v>133</v>
+      </c>
       <c r="I8" s="14"/>
       <c r="J8" s="14"/>
       <c r="K8" s="14"/>
@@ -48989,12 +49163,18 @@
       <c r="O8" s="14"/>
       <c r="P8" s="14"/>
       <c r="Q8" s="14"/>
-      <c r="R8" s="14"/>
+      <c r="R8" s="14" t="s">
+        <v>81</v>
+      </c>
       <c r="S8" s="14"/>
-      <c r="T8" s="14"/>
+      <c r="T8" s="14">
+        <v>1</v>
+      </c>
       <c r="U8" s="14"/>
       <c r="V8" s="14"/>
-      <c r="W8" s="14"/>
+      <c r="W8" s="14">
+        <v>1</v>
+      </c>
       <c r="X8" s="59"/>
       <c r="Y8" s="15"/>
     </row>
@@ -49162,12 +49342,18 @@
       <c r="B15" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="22"/>
-      <c r="D15" s="23"/>
+      <c r="C15" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="D15" s="23">
+        <v>1</v>
+      </c>
       <c r="E15" s="23"/>
       <c r="F15" s="23"/>
       <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
+      <c r="H15" s="23" t="s">
+        <v>134</v>
+      </c>
       <c r="I15" s="23"/>
       <c r="J15" s="23"/>
       <c r="K15" s="23"/>
@@ -49177,12 +49363,18 @@
       <c r="O15" s="23"/>
       <c r="P15" s="23"/>
       <c r="Q15" s="23"/>
-      <c r="R15" s="23"/>
+      <c r="R15" s="23" t="s">
+        <v>81</v>
+      </c>
       <c r="S15" s="23"/>
-      <c r="T15" s="23"/>
+      <c r="T15" s="23">
+        <v>1</v>
+      </c>
       <c r="U15" s="23"/>
       <c r="V15" s="23"/>
-      <c r="W15" s="23"/>
+      <c r="W15" s="23">
+        <v>0</v>
+      </c>
       <c r="X15" s="61"/>
       <c r="Y15" s="24"/>
     </row>
@@ -49190,27 +49382,39 @@
       <c r="B16" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="57"/>
-      <c r="D16" s="58"/>
+      <c r="C16" s="57">
+        <v>0</v>
+      </c>
+      <c r="D16" s="58">
+        <v>0</v>
+      </c>
       <c r="E16" s="27"/>
       <c r="F16" s="27"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
+      <c r="H16" s="28" t="s">
+        <v>128</v>
+      </c>
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
-      <c r="K16" s="56"/>
+      <c r="K16" s="23"/>
       <c r="L16" s="28"/>
       <c r="M16" s="28"/>
       <c r="N16" s="28"/>
       <c r="O16" s="28"/>
       <c r="P16" s="28"/>
       <c r="Q16" s="28"/>
-      <c r="R16" s="28"/>
+      <c r="R16" s="28">
+        <v>0</v>
+      </c>
       <c r="S16" s="28"/>
-      <c r="T16" s="28"/>
+      <c r="T16" s="28">
+        <v>0</v>
+      </c>
       <c r="U16" s="28"/>
       <c r="V16" s="28"/>
-      <c r="W16" s="56"/>
+      <c r="W16" s="56">
+        <v>1</v>
+      </c>
       <c r="X16" s="62"/>
       <c r="Y16" s="29"/>
     </row>
@@ -49614,17 +49818,29 @@
       <c r="C24" s="13"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
+      <c r="F24" s="14">
+        <v>3</v>
+      </c>
       <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
+      <c r="H24" s="14">
+        <v>92</v>
+      </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
+      <c r="K24" s="14">
+        <v>2</v>
+      </c>
+      <c r="L24" s="14">
+        <v>5</v>
+      </c>
+      <c r="M24" s="14">
+        <v>499</v>
+      </c>
       <c r="N24" s="14"/>
       <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="P24" s="14" t="s">
+        <v>83</v>
+      </c>
       <c r="Q24" s="14"/>
       <c r="R24" s="14"/>
       <c r="S24" s="14"/>
@@ -49800,17 +50016,29 @@
       <c r="C31" s="22"/>
       <c r="D31" s="23"/>
       <c r="E31" s="23"/>
-      <c r="F31" s="23"/>
+      <c r="F31" s="23">
+        <v>2</v>
+      </c>
       <c r="G31" s="23"/>
-      <c r="H31" s="23"/>
+      <c r="H31" s="23">
+        <v>45</v>
+      </c>
       <c r="I31" s="23"/>
       <c r="J31" s="23"/>
-      <c r="K31" s="23"/>
-      <c r="L31" s="23"/>
-      <c r="M31" s="23"/>
+      <c r="K31" s="23">
+        <v>2</v>
+      </c>
+      <c r="L31" s="23">
+        <v>3</v>
+      </c>
+      <c r="M31" s="23">
+        <v>113</v>
+      </c>
       <c r="N31" s="23"/>
       <c r="O31" s="23"/>
-      <c r="P31" s="23"/>
+      <c r="P31" s="23" t="s">
+        <v>135</v>
+      </c>
       <c r="Q31" s="23"/>
       <c r="R31" s="23"/>
       <c r="S31" s="23"/>
@@ -49828,17 +50056,29 @@
       <c r="C32" s="26"/>
       <c r="D32" s="27"/>
       <c r="E32" s="27"/>
-      <c r="F32" s="27"/>
+      <c r="F32" s="27">
+        <v>1</v>
+      </c>
       <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
+      <c r="H32" s="28">
+        <v>47</v>
+      </c>
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
+      <c r="K32" s="28">
+        <v>0</v>
+      </c>
+      <c r="L32" s="28">
+        <v>2</v>
+      </c>
+      <c r="M32" s="28">
+        <v>386</v>
+      </c>
       <c r="N32" s="28"/>
       <c r="O32" s="23"/>
-      <c r="P32" s="28"/>
+      <c r="P32" s="28">
+        <v>1</v>
+      </c>
       <c r="Q32" s="28"/>
       <c r="R32" s="28"/>
       <c r="S32" s="28"/>
@@ -49975,21 +50215,47 @@
       <c r="B36" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="C36" s="46"/>
-      <c r="D36" s="41"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
+      <c r="C36" s="46">
+        <v>3</v>
+      </c>
+      <c r="D36" s="41">
+        <v>2</v>
+      </c>
+      <c r="E36" s="42">
+        <v>15</v>
+      </c>
+      <c r="F36" s="42">
+        <v>270</v>
+      </c>
+      <c r="G36" s="42">
+        <v>42</v>
+      </c>
+      <c r="H36" s="42">
+        <v>5</v>
+      </c>
+      <c r="I36" s="42">
+        <v>3</v>
+      </c>
+      <c r="J36" s="42">
+        <v>1</v>
+      </c>
+      <c r="K36" s="42">
+        <v>11</v>
+      </c>
+      <c r="L36" s="42">
+        <v>2</v>
+      </c>
       <c r="M36" s="42"/>
       <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="43"/>
+      <c r="O36" s="42">
+        <v>9</v>
+      </c>
+      <c r="P36" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="43">
+        <v>3</v>
+      </c>
       <c r="R36" s="72"/>
       <c r="S36" s="44"/>
       <c r="T36" s="44"/>
@@ -50133,21 +50399,47 @@
       <c r="B42" s="45" t="s">
         <v>53</v>
       </c>
-      <c r="C42" s="46"/>
-      <c r="D42" s="41"/>
-      <c r="E42" s="42"/>
-      <c r="F42" s="42"/>
-      <c r="G42" s="42"/>
-      <c r="H42" s="42"/>
-      <c r="I42" s="42"/>
-      <c r="J42" s="42"/>
-      <c r="K42" s="42"/>
-      <c r="L42" s="42"/>
+      <c r="C42" s="46">
+        <v>3</v>
+      </c>
+      <c r="D42" s="41">
+        <v>2</v>
+      </c>
+      <c r="E42" s="42">
+        <v>15</v>
+      </c>
+      <c r="F42" s="42">
+        <v>270</v>
+      </c>
+      <c r="G42" s="42">
+        <v>42</v>
+      </c>
+      <c r="H42" s="42">
+        <v>5</v>
+      </c>
+      <c r="I42" s="42">
+        <v>3</v>
+      </c>
+      <c r="J42" s="42">
+        <v>1</v>
+      </c>
+      <c r="K42" s="42">
+        <v>11</v>
+      </c>
+      <c r="L42" s="42">
+        <v>2</v>
+      </c>
       <c r="M42" s="42"/>
       <c r="N42" s="42"/>
-      <c r="O42" s="42"/>
-      <c r="P42" s="42"/>
-      <c r="Q42" s="43"/>
+      <c r="O42" s="42">
+        <v>9</v>
+      </c>
+      <c r="P42" s="42">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="43">
+        <v>3</v>
+      </c>
       <c r="R42" s="91" t="s">
         <v>54</v>
       </c>
@@ -50189,7 +50481,10 @@
       <c r="B44" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="C44" s="99"/>
+      <c r="C44" s="99">
+        <f>14+1+1+47+2+386+1</f>
+        <v>452</v>
+      </c>
       <c r="D44" s="99"/>
       <c r="E44" s="99"/>
     </row>
@@ -50197,7 +50492,10 @@
       <c r="B45" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="C45" s="99"/>
+      <c r="C45" s="99">
+        <f>11</f>
+        <v>11</v>
+      </c>
       <c r="D45" s="99"/>
       <c r="E45" s="99"/>
     </row>

--- a/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
+++ b/GBDS APRIL FILES 2026/CSR MONTH OF APRIL 2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\GBDS APRIL FILES 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04B07B29-8AD7-477D-8856-EF692F5D0194}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F389AB9-C647-464B-AFEE-7F152269EBEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" firstSheet="24" activeTab="35" xr2:uid="{67C3A74A-A57E-4AB5-8CD3-31B592A14032}"/>
   </bookViews>
